--- a/localcsms/web/admin-web/src/main/resources/RC_007.xlsx
+++ b/localcsms/web/admin-web/src/main/resources/RC_007.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AntigravityProject\lh\localcsms\web\admin-web\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A92D9E-D95E-41A8-87E8-6D38EF997006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BAE259-54B0-4362-91CE-BDC1203178FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2190" yWindow="5260" windowWidth="24200" windowHeight="12660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3276" yWindow="4752" windowWidth="34560" windowHeight="18600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -94,9 +94,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="_-* #,##0_р_._-;\-* #,##0_р_._-;_-* &quot;-&quot;_р_._-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="0.00_);\(0.00\)"/>
     <numFmt numFmtId="178" formatCode="0_);\(0\)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
@@ -217,9 +216,6 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -227,6 +223,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -535,42 +534,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:J5"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="16" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.36328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.08984375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="28.81640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.1796875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="20" style="2" customWidth="1"/>
-    <col min="7" max="7" width="26.54296875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.1796875" style="1"/>
-    <col min="10" max="10" width="18.1796875" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.1796875" style="1"/>
+    <col min="7" max="7" width="26.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="26.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="18.21875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.21875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
     </row>
-    <row r="2" spans="2:10" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
+    <row r="2" spans="2:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
     </row>
-    <row r="3" spans="2:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:10" ht="17.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:10" ht="19.2" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
@@ -600,31 +600,31 @@
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="9" t="s">
         <v>18</v>
       </c>
     </row>
